--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484170_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484170_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5786</v>
+        <v>9.714600000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7413</v>
+        <v>5.7469</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8374</v>
+        <v>3.9676</v>
       </c>
       <c r="G2" t="n">
         <v>8.133100000000001</v>
@@ -610,13 +610,13 @@
         <v>3.1741</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0922</v>
+        <v>0.2281</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3772</v>
+        <v>-1.3716</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4694</v>
+        <v>1.5996</v>
       </c>
       <c r="V2" t="n">
         <v>2.1469</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5507</v>
+        <v>7.0883</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3738</v>
+        <v>5.8272</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1769</v>
+        <v>1.2611</v>
       </c>
       <c r="G3" t="n">
         <v>6.0302</v>
@@ -688,13 +688,13 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.539</v>
+        <v>-0.0014</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4963</v>
+        <v>-1.0428</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9572000000000001</v>
+        <v>1.0414</v>
       </c>
       <c r="V3" t="n">
         <v>0.266</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0563</v>
+        <v>2.2714</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5006</v>
+        <v>0.6877</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5557</v>
+        <v>1.5837</v>
       </c>
       <c r="G4" t="n">
         <v>1.6631</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4518</v>
+        <v>-0.2367</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0599</v>
+        <v>-0.8728</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6081</v>
+        <v>0.6362</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9405</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3388</v>
+        <v>1.9925</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7023</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6364</v>
+        <v>1.0011</v>
       </c>
       <c r="G5" t="n">
         <v>3.3737</v>
@@ -844,13 +844,13 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9755</v>
+        <v>-0.3217</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1222</v>
+        <v>-0.8331</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1468</v>
+        <v>0.5115</v>
       </c>
       <c r="V5" t="n">
         <v>-0.266</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9858</v>
+        <v>1.4307</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2707</v>
+        <v>1.4351</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2849</v>
+        <v>-0.0043</v>
       </c>
       <c r="G6" t="n">
         <v>2.0959</v>
@@ -922,13 +922,13 @@
         <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0939</v>
+        <v>-0.649</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9352</v>
+        <v>-0.7708</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1587</v>
+        <v>0.1218</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2065</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. FEIXA MORANCHO</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5863</v>
+        <v>0.9542</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1087</v>
+        <v>-2.1366</v>
       </c>
       <c r="F7" t="n">
-        <v>0.695</v>
+        <v>3.0909</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2577</v>
+        <v>2.0563</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5142</v>
+        <v>0.9926</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2565</v>
+        <v>1.0637</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1406</v>
+        <v>1.5419</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0202</v>
+        <v>1.3009</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>0.241</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3983</v>
+        <v>0.5144</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5344</v>
+        <v>-0.3083</v>
       </c>
       <c r="O7" t="n">
-        <v>0.136</v>
+        <v>0.8227</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1695</v>
+        <v>-0.1616</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2494</v>
+        <v>-1.0202</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4188</v>
+        <v>0.8586</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6745</v>
+        <v>-0.9405</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>P. FEIXA MORANCHO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5467</v>
+        <v>0.3899</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.488</v>
+        <v>-0.1087</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0348</v>
+        <v>0.4986</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0563</v>
+        <v>-0.2577</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9926</v>
+        <v>-0.5142</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0637</v>
+        <v>0.2565</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5419</v>
+        <v>0.1406</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3009</v>
+        <v>0.0202</v>
       </c>
       <c r="L8" t="n">
-        <v>0.241</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5144</v>
+        <v>-0.3983</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3083</v>
+        <v>-0.5344</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8227</v>
+        <v>0.136</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9838</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.0269</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3716</v>
+        <v>-0.2494</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8025</v>
+        <v>0.2224</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9405</v>
+        <v>0.6745</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3338</v>
+        <v>0.1189</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2832</v>
+        <v>-0.5285</v>
       </c>
       <c r="F9" t="n">
-        <v>0.617</v>
+        <v>0.6474</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4597</v>
+        <v>-0.2216</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-1.1388</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7294</v>
+        <v>0.9172</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0679</v>
+        <v>-0.0298</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.468</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5999</v>
+        <v>0.6451</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3918</v>
+        <v>-0.1918</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2623</v>
+        <v>-0.4639</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1295</v>
+        <v>0.2721</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7935</v>
+        <v>-0.3854</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1814</v>
+        <v>-0.4988</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6121</v>
+        <v>0.1133</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6032</v>
+        <v>-0.266</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.118</v>
+        <v>-0.3548</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6532</v>
+        <v>-0.6913</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5352</v>
+        <v>0.3365</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2216</v>
+        <v>-1.4597</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1388</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9172</v>
+        <v>-0.7294</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0298</v>
+        <v>-1.0679</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.468</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6451</v>
+        <v>-0.5999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1918</v>
+        <v>-0.3918</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4639</v>
+        <v>-0.2623</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2721</v>
+        <v>-0.1295</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6223</v>
+        <v>0.1049</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.2267</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0011</v>
+        <v>0.3315</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4466</v>
+        <v>-0.3562</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9707</v>
+        <v>-0.9083</v>
       </c>
       <c r="F11" t="n">
-        <v>0.524</v>
+        <v>0.5521</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6556</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1797</v>
+        <v>-0.0893</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4364</v>
+        <v>-0.3741</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2567</v>
+        <v>0.2848</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6032</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8877</v>
+        <v>-1.555</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8571</v>
+        <v>-0.6928</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0306</v>
+        <v>-0.8622</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0943</v>
@@ -1390,13 +1390,13 @@
         <v>1.3887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7096</v>
+        <v>-0.3769</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6858</v>
+        <v>-0.5214</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0238</v>
+        <v>0.1445</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4724</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1515</v>
+        <v>-2.7626</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8749</v>
+        <v>-3.7106</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7235</v>
+        <v>0.9479</v>
       </c>
       <c r="G13" t="n">
         <v>-3.5987</v>
@@ -1468,13 +1468,13 @@
         <v>1.9838</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8819</v>
+        <v>-0.4931</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.8331</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1156</v>
+        <v>0.34</v>
       </c>
       <c r="V13" t="n">
         <v>0.3373</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.3732</v>
+        <v>18.9319</v>
       </c>
       <c r="E14" t="n">
-        <v>4.352899999999998</v>
+        <v>5.911500000000002</v>
       </c>
       <c r="F14" t="n">
         <v>13.0204</v>
       </c>
       <c r="G14" t="n">
-        <v>16.0647</v>
+        <v>16.06469999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-9.999999999976694e-05</v>
@@ -1546,13 +1546,13 @@
         <v>16.8626</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.9676</v>
+        <v>-2.409</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.1736</v>
+        <v>-8.614799999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>6.2058</v>
+        <v>6.2056</v>
       </c>
       <c r="V14" t="n">
         <v>-1.6672</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6314</v>
+        <v>1.8789</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7704</v>
+        <v>4.1582</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1391</v>
+        <v>-2.2793</v>
       </c>
       <c r="G15" t="n">
         <v>-1.6079</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6296</v>
+        <v>0.8771</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1359</v>
+        <v>-0.7481</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7655</v>
+        <v>1.6252</v>
       </c>
       <c r="V15" t="n">
         <v>1.6178</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.6907</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7849</v>
+        <v>0.4788</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0997</v>
+        <v>0.2119</v>
       </c>
       <c r="G16" t="n">
         <v>0.4692</v>
@@ -1702,13 +1702,13 @@
         <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6813</v>
+        <v>0.4874</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0679</v>
+        <v>-0.374</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7493</v>
+        <v>0.8615</v>
       </c>
       <c r="V16" t="n">
         <v>-0.266</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>A. NUÑEZ NAVARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2258</v>
+        <v>0.2684</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1307</v>
+        <v>-0.4855</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3565</v>
+        <v>0.754</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.9534</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8162</v>
+        <v>-0.5492</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4368</v>
+        <v>-0.4042</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3121</v>
+        <v>-0.2467</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3279</v>
+        <v>-0.3672</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.64</v>
+        <v>0.1205</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3084</v>
+        <v>-0.7067</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4883</v>
+        <v>-0.1821</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7967</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1814</v>
+        <v>-0.255</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1206</v>
+        <v>1.0858</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X17" t="n">
         <v>-0.1206</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. NUÑEZ NAVARRO</t>
+          <t>B. PAÑART POSTIGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1868</v>
+        <v>0.1557</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7916</v>
+        <v>-0.9862</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9784</v>
+        <v>1.1419</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9534</v>
+        <v>1.7403</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5492</v>
+        <v>1.8141</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4042</v>
+        <v>-0.0738</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2467</v>
+        <v>2.911</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3672</v>
+        <v>2.8682</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1205</v>
+        <v>0.0427</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7067</v>
+        <v>-1.1707</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1821</v>
+        <v>-1.0541</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.1165</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3968</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1903</v>
+        <v>-3.1741</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4511</v>
+        <v>0.2721</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5611</v>
+        <v>-0.6518</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0122</v>
+        <v>0.9238</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0858</v>
+        <v>-0.0713</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2065</v>
+        <v>-0.0713</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. PAÑART POSTIGO</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5891</v>
+        <v>0.0779</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3943</v>
+        <v>-0.3348</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8052</v>
+        <v>0.4126</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7403</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8141</v>
+        <v>0.8162</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0738</v>
+        <v>-1.4368</v>
       </c>
       <c r="J19" t="n">
-        <v>2.911</v>
+        <v>-0.3121</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8682</v>
+        <v>0.3279</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0427</v>
+        <v>-0.64</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1707</v>
+        <v>-0.3084</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0541</v>
+        <v>0.4883</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1165</v>
+        <v>-0.7967</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4727</v>
+        <v>0.6207</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0599</v>
+        <v>-0.0226</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.6433</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0713</v>
+        <v>-0.1206</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4077</v>
+        <v>-1.5123</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2571</v>
+        <v>-2.053</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8494</v>
+        <v>0.5407</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9582000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.1984</v>
       </c>
       <c r="S20" t="n">
-        <v>0.344</v>
+        <v>0.2395</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6858</v>
+        <v>-0.4817</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0298</v>
+        <v>0.7212</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1637</v>
+        <v>-3.4008</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5335</v>
+        <v>-3.3497</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3698</v>
+        <v>-0.051</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4556</v>
@@ -2092,13 +2092,13 @@
         <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>1.879</v>
+        <v>0.6419</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0112</v>
+        <v>-0.8274</v>
       </c>
       <c r="U21" t="n">
-        <v>1.8902</v>
+        <v>1.4693</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3547</v>
+        <v>-3.7859</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9879</v>
+        <v>-1.7838</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3668</v>
+        <v>-2.0021</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7311</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7544</v>
+        <v>-0.1856</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1222</v>
+        <v>-0.9182</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3678</v>
+        <v>0.7326</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8692</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9197</v>
+        <v>-5.3534</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9459</v>
+        <v>-4.4358</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9737</v>
+        <v>-0.9176</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0562</v>
@@ -2248,13 +2248,13 @@
         <v>1.3887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2233</v>
+        <v>0.3429</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.621</v>
+        <v>-1.1108</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3977</v>
+        <v>1.4538</v>
       </c>
       <c r="V23" t="n">
         <v>0.1453</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.8668</v>
+        <v>-6.3924</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5347</v>
+        <v>-4.2286</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3321</v>
+        <v>-2.1638</v>
       </c>
       <c r="G24" t="n">
         <v>-4.8912</v>
@@ -2326,13 +2326,13 @@
         <v>1.1903</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3355</v>
+        <v>0.1389</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1222</v>
+        <v>-0.8161</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7867</v>
+        <v>0.955</v>
       </c>
       <c r="V24" t="n">
         <v>0.1453</v>
@@ -2359,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.3731</v>
+        <v>-17.3732</v>
       </c>
       <c r="E25" t="n">
         <v>-13.0204</v>
@@ -2371,7 +2371,7 @@
         <v>-16.0646</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.999999999965592e-05</v>
+        <v>-0.0001000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-16.0646</v>
@@ -2383,7 +2383,7 @@
         <v>4.1646</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1299000000000003</v>
+        <v>-0.1299000000000006</v>
       </c>
       <c r="M25" t="n">
         <v>-20.0994</v>
@@ -2407,10 +2407,10 @@
         <v>3.9677</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.205800000000001</v>
+        <v>-6.2057</v>
       </c>
       <c r="U25" t="n">
-        <v>10.1736</v>
+        <v>10.1735</v>
       </c>
       <c r="V25" t="n">
         <v>1.6671</v>
